--- a/eduservices/COCKPIT_20260910_corrige.xlsx
+++ b/eduservices/COCKPIT_20260910_corrige.xlsx
@@ -15,7 +15,7 @@
     <definedName name="Query01" localSheetId="1" comment="Query01">Cockpit!$AK$6:$AN$11</definedName>
     <definedName name="Query00" localSheetId="1" comment="Query00">Cockpit!$AD$6:$AH$11</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -565,7 +565,7 @@
     <t>LE COMPTE D'EXPLOITATION, POSTE PAR POSTE</t>
   </si>
   <si>
-    <t>Variation</t>
+    <t>Effet EBITDA</t>
   </si>
   <si>
     <t>Part des charges</t>
@@ -574,7 +574,7 @@
     <t/>
   </si>
   <si>
-    <t>Contrôle</t>
+    <t>= EBITDA  ·  produits − charges − siège</t>
   </si>
   <si>
     <t>RAPPROCHEMENT DU CHIFFRE D'AFFAIRES  ·  comptes de produit contre socle CRM</t>
@@ -18565,7 +18565,7 @@
     <col min="2" max="2" width="2.421875" customWidth="1"/>
     <col min="3" max="3" width="9.00390625" customWidth="1"/>
     <col min="4" max="4" width="16.00390625" customWidth="1"/>
-    <col min="5" max="5" width="36.00390625" customWidth="1"/>
+    <col min="5" max="5" width="47" customWidth="1"/>
     <col min="6" max="7" width="15.00390625" customWidth="1"/>
     <col min="8" max="8" width="14.00390625" customWidth="1"/>
     <col min="9" max="9" width="15.00390625" customWidth="1"/>
@@ -18644,8 +18644,7 @@
     <row r="6" ht="24" customHeight="1">
       <c r="B6" s="99"/>
       <c r="C6" s="126" t="str">
-        <f>"Sur "&amp;TEXT(G35,"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(G36:G48),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(G35:G48),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(G35:G48)/G35,"0.0%")&amp;" du chiffre d'affaires."</f>
-        <v>Sur 3.306.675 € de chiffre d'affaires, -4.333.386 € partent en charges. Il reste 7.640.061 € d'EBITDA, soit 231,0% du chiffre d'affaires.</v>
+        <f>"Sur "&amp;TEXT(SUM(G35:G37),"#,##0 €")&amp;" de chiffre d'affaires, "&amp;TEXT(-SUM(G38:G50),"#,##0 €")&amp;" partent en charges. Il reste "&amp;TEXT(SUM(G35:G50),"#,##0 €")&amp;" d'EBITDA, soit "&amp;TEXT(SUM(G35:G50)/SUM(G35:G37),"0.0%")&amp;" du chiffre d'affaires."</f>
       </c>
       <c r="D6" s="99"/>
       <c r="E6" s="99"/>
@@ -19478,7 +19477,7 @@
         <v>186675</v>
       </c>
       <c r="I35" s="134" t="str">
-        <f>IF($D35="Produits","",-G35/SUM(G38:G50))</f>
+        <f>IF($D35="Produits","",G35/SUM($G$38:$G$50))</f>
         <v/>
       </c>
       <c r="J35" s="99"/>
@@ -19514,7 +19513,7 @@
         <v>1147240</v>
       </c>
       <c r="I36" s="134" t="str">
-        <f>IF($D36="Produits","",-G36/SUM(G38:G50))</f>
+        <f>IF($D36="Produits","",G36/SUM($G$38:$G$50))</f>
         <v/>
       </c>
       <c r="J36" s="99"/>
@@ -19550,7 +19549,7 @@
         <v>6300</v>
       </c>
       <c r="I37" s="134" t="str">
-        <f>IF($D37="Produits","",-G37/SUM(G38:G50))</f>
+        <f>IF($D37="Produits","",G37/SUM($G$38:$G$50))</f>
         <v/>
       </c>
       <c r="J37" s="99"/>
@@ -19586,7 +19585,7 @@
         <v>-72055</v>
       </c>
       <c r="I38" s="134">
-        <f>IF($D38="Produits","",-G38/SUM(G38:G50))</f>
+        <f>IF($D38="Produits","",G38/SUM($G$38:$G$50))</f>
         <v>-0.0821450817934761</v>
       </c>
       <c r="J38" s="99"/>
@@ -19630,7 +19629,7 @@
         <v>-30880</v>
       </c>
       <c r="I39" s="134">
-        <f>IF($D39="Produits","",-G39/SUM(G38:G50))</f>
+        <f>IF($D39="Produits","",G39/SUM($G$38:$G$50))</f>
         <v>-0.0352049905347983</v>
       </c>
       <c r="J39" s="99"/>
@@ -19674,7 +19673,7 @@
         <v>-20588</v>
       </c>
       <c r="I40" s="134">
-        <f>IF($D40="Produits","",-G40/SUM(G38:G50))</f>
+        <f>IF($D40="Produits","",G40/SUM($G$38:$G$50))</f>
         <v>-0.0234700975688122</v>
       </c>
       <c r="J40" s="99"/>
@@ -19718,7 +19717,7 @@
         <v>-39472</v>
       </c>
       <c r="I41" s="134">
-        <f>IF($D41="Produits","",-G41/SUM(G38:G50))</f>
+        <f>IF($D41="Produits","",G41/SUM($G$38:$G$50))</f>
         <v>-0.0225507688909773</v>
       </c>
       <c r="J41" s="99"/>
@@ -19762,7 +19761,7 @@
         <v>-175278.51</v>
       </c>
       <c r="I42" s="134">
-        <f>IF($D42="Produits","",-G42/SUM(G38:G50))</f>
+        <f>IF($D42="Produits","",G42/SUM($G$38:$G$50))</f>
         <v>-0.199503144490327</v>
       </c>
       <c r="J42" s="99"/>
@@ -19806,7 +19805,7 @@
         <v>-92457.5800000001</v>
       </c>
       <c r="I43" s="134">
-        <f>IF($D43="Produits","",-G43/SUM(G38:G50))</f>
+        <f>IF($D43="Produits","",G43/SUM($G$38:$G$50))</f>
         <v>-0.105610120457586</v>
       </c>
       <c r="J43" s="99"/>
@@ -19850,7 +19849,7 @@
         <v>-143820.44</v>
       </c>
       <c r="I44" s="134">
-        <f>IF($D44="Produits","",-G44/SUM(G38:G50))</f>
+        <f>IF($D44="Produits","",G44/SUM($G$38:$G$50))</f>
         <v>-0.164282367472006</v>
       </c>
       <c r="J44" s="99"/>
@@ -19894,7 +19893,7 @@
         <v>-108255.67</v>
       </c>
       <c r="I45" s="134">
-        <f>IF($D45="Produits","",-G45/SUM(G38:G50))</f>
+        <f>IF($D45="Produits","",G45/SUM($G$38:$G$50))</f>
         <v>-0.123222427610891</v>
       </c>
       <c r="J45" s="99"/>
@@ -19938,7 +19937,7 @@
         <v>-15464.58</v>
       </c>
       <c r="I46" s="134">
-        <f>IF($D46="Produits","",-G46/SUM(G38:G50))</f>
+        <f>IF($D46="Produits","",G46/SUM($G$38:$G$50))</f>
         <v>-0.0176030863386056</v>
       </c>
       <c r="J46" s="99"/>
@@ -19982,7 +19981,7 @@
         <v>-10271.85</v>
       </c>
       <c r="I47" s="134">
-        <f>IF($D47="Produits","",-G47/SUM(G38:G50))</f>
+        <f>IF($D47="Produits","",G47/SUM($G$38:$G$50))</f>
         <v>-0.0117344997841731</v>
       </c>
       <c r="J47" s="99"/>
@@ -20026,7 +20025,7 @@
         <v>-15412.24</v>
       </c>
       <c r="I48" s="134">
-        <f>IF($D48="Produits","",-G48/SUM(G38:G50))</f>
+        <f>IF($D48="Produits","",G48/SUM($G$38:$G$50))</f>
         <v>-0.0176017878517725</v>
       </c>
       <c r="J48" s="99"/>
@@ -20070,7 +20069,7 @@
         <v>-10309.08</v>
       </c>
       <c r="I49" s="134">
-        <f>IF($D49="Produits","",-G49/SUM(G38:G50))</f>
+        <f>IF($D49="Produits","",G49/SUM($G$38:$G$50))</f>
         <v>-0.0117354097637457</v>
       </c>
       <c r="J49" s="99"/>
@@ -20114,7 +20113,7 @@
         <v>-227927.085198</v>
       </c>
       <c r="I50" s="134">
-        <f>IF($D50="Produits","",-G50/SUM(G38:G50))</f>
+        <f>IF($D50="Produits","",G50/SUM($G$38:$G$50))</f>
         <v>-0.185336217442829</v>
       </c>
       <c r="J50" s="99"/>
@@ -21604,7 +21603,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:H50">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan" text="null">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan" text="null">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
